--- a/excel/shuwa_exam_question_list_ver0.04.xlsx
+++ b/excel/shuwa_exam_question_list_ver0.04.xlsx
@@ -15458,7 +15458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15.75"/>
   <cols>
     <col width="9" customWidth="1" style="5" min="1" max="4"/>
@@ -16308,53 +16308,10 @@
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
-          <t>次の語のうちで1つだけ両手を使わない手話表現があります。それはどれですか。</t>
+          <t>次の言葉を手話で表現した時、両手の形が異なるものはどれですか。</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1. 気温
-2. プライバシー
-3. オーバー
-4. 詳細</t>
-        </is>
-      </c>
-      <c r="G20" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="H20" s="11" t="inlineStr">
-        <is>
-          <t>2. プライバシー。全日本ろうあ連盟発行「わたしたちの手話 学習辞典1」などを参照。</t>
-        </is>
-      </c>
-      <c r="I20" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="63" customHeight="1">
-      <c r="A21" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B21" s="1" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C21" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>4択問題</t>
-        </is>
-      </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>次の言葉を手話で表現した時、両手の形が異なるものはどれですか。</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>1. 生きる
 2. 訓練
@@ -16362,12 +16319,55 @@
 4. 材料</t>
         </is>
       </c>
+      <c r="G20" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>3. 基準。【基準】以外はすべて両手こぶしを使った手話表現です。</t>
+        </is>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="63" customHeight="1">
+      <c r="A21" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>4択問題</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>手話表現した時漢字の字形を表現していないものはどれですか。</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1. 災害
+2. 非
+3. 入る
+4. 虹</t>
+        </is>
+      </c>
       <c r="G21" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>3. 基準。【基準】以外はすべて両手こぶしを使った手話表現です。</t>
+          <t>4. 虹。【虹】の手話は事象そのものから成り立っています。ちなみに虹を七色と認識しているのは日本の特徴のようです。</t>
         </is>
       </c>
       <c r="I21" s="1" t="inlineStr">
@@ -16394,53 +16394,10 @@
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>手話表現した時漢字の字形を表現していないものはどれですか。</t>
+          <t>耳で聞く音は空気の振動によって伝わります。次の中で音の3要素ではないものはどれですか。</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>1. 災害
-2. 非
-3. 北陸
-4. 虹</t>
-        </is>
-      </c>
-      <c r="G22" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="H22" s="11" t="inlineStr">
-        <is>
-          <t>4. 虹。【虹】の手話は事象そのものから成り立っています。ちなみに虹を七色と認識しているのは日本の特徴のようです。</t>
-        </is>
-      </c>
-      <c r="I22" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="63" customHeight="1">
-      <c r="A23" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B23" s="1" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C23" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>4択問題</t>
-        </is>
-      </c>
-      <c r="E23" s="1" t="inlineStr">
-        <is>
-          <t>耳で聞く音は空気の振動によって伝わります。次の中で音の3要素ではないものはどれですか。</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>1. 音の大きさ
 2. 音の長さ
@@ -16448,42 +16405,42 @@
 4. 音色</t>
         </is>
       </c>
-      <c r="G23" s="1" t="n">
+      <c r="G22" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="H23" s="11" t="inlineStr">
+      <c r="H22" s="11" t="inlineStr">
         <is>
           <t>2. 音の長さ。音の三要素は「音の高さ」「音の大きさ」「音色」の３つからなります。</t>
         </is>
       </c>
-      <c r="I23" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="63" customHeight="1">
-      <c r="A24" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B24" s="1" t="n">
+      <c r="I22" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="63" customHeight="1">
+      <c r="A23" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B23" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C23" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="1" t="inlineStr">
+      <c r="D23" s="1" t="inlineStr">
         <is>
           <t>4択問題</t>
         </is>
       </c>
-      <c r="E24" s="1" t="inlineStr">
+      <c r="E23" s="1" t="inlineStr">
         <is>
           <t>手話が言語であることについて「言語（手話を含む。）」と条文の一節に規定した法律はなんですか。</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>1. 障害者基本法
 2. 障害者差別解消法
@@ -16491,42 +16448,42 @@
 4. 障害者自立支援法</t>
         </is>
       </c>
-      <c r="G24" s="1" t="n">
+      <c r="G23" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H24" s="11" t="inlineStr">
+      <c r="H23" s="11" t="inlineStr">
         <is>
           <t>1. 障害者基本法。2011年の障害者基本法改正で第3条第11項第3号に規定されたことによって言語性が認められたといわれています。</t>
         </is>
       </c>
-      <c r="I24" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="63" customHeight="1">
-      <c r="A25" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B25" s="1" t="n">
+      <c r="I23" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="63" customHeight="1">
+      <c r="A24" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B24" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C24" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="1" t="inlineStr">
+      <c r="D24" s="1" t="inlineStr">
         <is>
           <t>4択問題</t>
         </is>
       </c>
-      <c r="E25" s="1" t="inlineStr">
+      <c r="E24" s="1" t="inlineStr">
         <is>
           <t>聴覚障害者のために認定NPO法人障害者放送通信機構が提供している手話と字幕付きで視聴できる番組はなんですか。</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>1. 目で見るテレビ
 2. 目で聴くテレビ
@@ -16534,42 +16491,42 @@
 4. 耳で聴くテレビ</t>
         </is>
       </c>
-      <c r="G25" s="1" t="n">
+      <c r="G24" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="H25" s="11" t="inlineStr">
+      <c r="H24" s="11" t="inlineStr">
         <is>
           <t>2. 目で聴くテレビ。1995年の阪神淡路大震災の反省を踏まえて1998年から手話と字幕を付けた目で聴くテレビがスタートしました。</t>
         </is>
       </c>
-      <c r="I25" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="63" customHeight="1">
-      <c r="A26" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B26" s="1" t="n">
+      <c r="I24" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="63" customHeight="1">
+      <c r="A25" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B25" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C25" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="1" t="inlineStr">
+      <c r="D25" s="1" t="inlineStr">
         <is>
           <t>4択問題</t>
         </is>
       </c>
-      <c r="E26" s="1" t="inlineStr">
+      <c r="E25" s="1" t="inlineStr">
         <is>
           <t>障害の社会的障壁について障害があるものにとって日常生活または社会生活を営む上で障壁となるような社会における事物、制度、慣行、観念、その他の一切のものをいうと定義づけている。これはどんな視点を取り入れたものですか。</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>1. バリアフリー
 2. 社会モデル
@@ -16577,44 +16534,44 @@
 4. リハビリテーション</t>
         </is>
       </c>
-      <c r="G26" s="1" t="n">
+      <c r="G25" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="H26" s="11" t="inlineStr">
+      <c r="H25" s="11" t="inlineStr">
         <is>
           <t>2. 社会モデル。社会的障壁の定義は「社会モデル」の視点に基づいています。社会モデルとは、障害は個人の心身機能ではなく、社会の側にある障壁（バリア）によって生じるという考え方です。バリアフリーは障壁を除去する取り組みのことであり、視点・考え方そのものではありません。</t>
         </is>
       </c>
-      <c r="I26" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="157.5" customHeight="1">
-      <c r="A27" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B27" s="1" t="n">
+      <c r="I25" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="63" customHeight="1">
+      <c r="A26" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B26" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>準1</t>
         </is>
       </c>
-      <c r="D27" s="1" t="inlineStr">
+      <c r="D26" s="1" t="inlineStr">
         <is>
           <t>穴埋め形式</t>
         </is>
       </c>
-      <c r="E27" s="1" t="inlineStr">
+      <c r="E26" s="1" t="inlineStr">
         <is>
           <t>（ア）難聴の場合は、音を（イ）に伝える部分の障害のため音が小さくなってしまいますが（イ）に異常がない場合は（ウ）で十分に大きな音に増幅すれば聞き取りは改善されます。（ウ）の装用効果がかなり（エ）と言えます。</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>1. 中耳
 2. 内耳
@@ -16628,46 +16585,46 @@
 10. 突発性</t>
         </is>
       </c>
-      <c r="G27" s="1" t="inlineStr">
+      <c r="G26" s="1" t="inlineStr">
         <is>
           <t>8,2,4,7</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="H26" s="11" t="inlineStr">
         <is>
           <t>(ア): 8. 伝音声 (イ): 2. 内耳 (ウ): 4. 補聴器 (エ): 7. 高い。伝音性難聴は空気の振動としての音を内耳に伝える外耳道、鼓膜、耳小骨の部分に障害があるため、振動が伝わりに肉なって音が小さく聞こえる障害です。</t>
         </is>
       </c>
-      <c r="I27" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="126" customHeight="1">
-      <c r="A28" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B28" s="1" t="n">
+      <c r="I26" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="157.5" customHeight="1">
+      <c r="A27" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B27" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>準1</t>
         </is>
       </c>
-      <c r="D28" s="1" t="inlineStr">
+      <c r="D27" s="1" t="inlineStr">
         <is>
           <t>穴埋め形式</t>
         </is>
       </c>
-      <c r="E28" s="1" t="inlineStr">
+      <c r="E27" s="1" t="inlineStr">
         <is>
           <t>日本では1878年、京都に（ア）が設立されました。手話はろう児の集団形成とともに（イ）を通じて形成され、ろう者の集団の中で発展したものと考えられます。この時代は聞こえないという障害ゆえに（ウ）や社会的偏見がありました。</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>1. 盲唖院
 2. ろうあ協会
@@ -16679,46 +16636,46 @@
 8. 自然</t>
         </is>
       </c>
-      <c r="G28" s="1" t="inlineStr">
+      <c r="G27" s="1" t="inlineStr">
         <is>
           <t>1,6,7</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="H27" s="11" t="inlineStr">
         <is>
           <t>(ア): 1. 盲唖院 (イ): 6. 教育 (ウ): 7. 差別。日本最初の聾学校として1878年に京都盲唖院、1880年には東京に訓盲院が設立され、教育の場で手話が取り入れられました。</t>
         </is>
       </c>
-      <c r="I28" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="126" customHeight="1">
-      <c r="A29" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B29" s="1" t="n">
+      <c r="I27" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="126" customHeight="1">
+      <c r="A28" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B28" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>準1</t>
         </is>
       </c>
-      <c r="D29" s="1" t="inlineStr">
+      <c r="D28" s="1" t="inlineStr">
         <is>
           <t>穴埋め形式</t>
         </is>
       </c>
-      <c r="E29" s="1" t="inlineStr">
+      <c r="E28" s="1" t="inlineStr">
         <is>
           <t>2022年5月に障害者情報アクセシビリティ・コミュニケーション施策推進法が施行されました。この法律はすべての障害者があらゆる分野の（ア）に参加するためには情報の十分な取得利用や（イ）意思疎通が極めて重要であることから障害者による情報の十分な取得利用や（イ）意思疎通が極めて重要であることから障害者による情報の取得利用・意思疎通にかかる施策を総合的に推進し、（ウ）の実現に資するために制定されました。</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>1. 仕事
 2. 集会
@@ -16730,46 +16687,46 @@
 8. 共生社会</t>
         </is>
       </c>
-      <c r="G29" s="1" t="inlineStr">
+      <c r="G28" s="1" t="inlineStr">
         <is>
           <t>3,4,8</t>
         </is>
       </c>
-      <c r="H29" s="11" t="inlineStr">
+      <c r="H28" s="11" t="inlineStr">
         <is>
           <t>(ア): 3. 活動 (イ): 4. 円滑な (ウ): 8. 共生社会。この法律の目的は「すべての障害者があらゆる分野の活動に参加するためにはその必要とする情報の十分な取得利用・円滑な意思疎通が極めて重要であり、障害者による情報の取得利用・意思疎通にかかる施策を総合的に推進し、共生社会の実現に資する」こととされています。</t>
         </is>
       </c>
-      <c r="I29" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="126" customHeight="1">
-      <c r="A30" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B30" s="1" t="n">
+      <c r="I28" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="126" customHeight="1">
+      <c r="A29" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B29" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>準1</t>
         </is>
       </c>
-      <c r="D30" s="1" t="inlineStr">
+      <c r="D29" s="1" t="inlineStr">
         <is>
           <t>穴埋め形式</t>
         </is>
       </c>
-      <c r="E30" s="1" t="inlineStr">
+      <c r="E29" s="1" t="inlineStr">
         <is>
           <t>手話の【夜】と【～なる】では（ア）が異なり、【思う】と【心】では（イ）が異なります。また【裁判】と【人事異動】では（ウ）が異なります。このような例から手話という言語は一定の要素が複雑に組み合わさって構成されているといえます。</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>1. 手話の位置
 2. 手指の動き
@@ -16781,46 +16738,46 @@
 8. 手のひらの向き</t>
         </is>
       </c>
-      <c r="G30" s="1" t="inlineStr">
+      <c r="G29" s="1" t="inlineStr">
         <is>
           <t>8,1,2</t>
         </is>
       </c>
-      <c r="H30" s="11" t="inlineStr">
+      <c r="H29" s="11" t="inlineStr">
         <is>
           <t>(ア): 8. 手のひらの向き (イ): 1. 手話の位置 (ウ): 2. 手指の動き。全日本ろうあ連盟発行「わたしたちの手話 学習辞典1」などを参照。</t>
         </is>
       </c>
-      <c r="I30" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="126" customHeight="1">
-      <c r="A31" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B31" s="1" t="n">
+      <c r="I29" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="126" customHeight="1">
+      <c r="A30" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B30" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>準1</t>
         </is>
       </c>
-      <c r="D31" s="1" t="inlineStr">
+      <c r="D30" s="1" t="inlineStr">
         <is>
           <t>穴埋め形式</t>
         </is>
       </c>
-      <c r="E31" s="1" t="inlineStr">
+      <c r="E30" s="1" t="inlineStr">
         <is>
           <t>（ア）が1969年に発行した「わたしたちの手話」は手話を（イ）で紹介したわが国では初めての本格的な手話単語集でした。それは（ウ）として位置づけられています。</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>1. 全国手話研修センター
 2. 全国手話通訳問題研究会
@@ -16832,46 +16789,46 @@
 8. 標準手話</t>
         </is>
       </c>
-      <c r="G31" s="1" t="inlineStr">
+      <c r="G30" s="1" t="inlineStr">
         <is>
           <t>3,4,8</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr">
+      <c r="H30" s="11" t="inlineStr">
         <is>
           <t>(ア): 3. 全日本ろうあ連盟 (イ): 4. イラスト (ウ): 8. 標準手話。標準手話の全国的な普及と手話サークルの発展に貢献し、日本手話研究所設立への流れを作りました。</t>
         </is>
       </c>
-      <c r="I31" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="126" customHeight="1">
-      <c r="A32" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B32" s="1" t="n">
+      <c r="I30" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="126" customHeight="1">
+      <c r="A31" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B31" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>準1</t>
         </is>
       </c>
-      <c r="D32" s="1" t="inlineStr">
+      <c r="D31" s="1" t="inlineStr">
         <is>
           <t>穴埋め形式</t>
         </is>
       </c>
-      <c r="E32" s="1" t="inlineStr">
+      <c r="E31" s="1" t="inlineStr">
         <is>
           <t>（ア）の交付があれば、障害福祉の窓口に申請することで（イ）の交付を受けられます。しかし、両耳の聴力レベルが（ウ）未満の場合は（ア）が交付されないため制度の対象外となり、全額自己負担となります。</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>1. 障害者年金手帳
 2. 身体障害者手帳
@@ -16883,46 +16840,46 @@
 8. 70デシベル</t>
         </is>
       </c>
-      <c r="G32" s="1" t="inlineStr">
+      <c r="G31" s="1" t="inlineStr">
         <is>
           <t>2,5,8</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="H31" s="11" t="inlineStr">
         <is>
           <t>(ア): 2. 身体障害者手帳 (イ): 5. 補聴器 (ウ): 8. 70デシベル。現在、軽度・中度難聴者に対する補聴器購入費助成に取り組む自治体は増えていますが、少ない状況です。対象年齢が全年齢・65歳以上、18歳以上など自治体によってばらばらです。</t>
         </is>
       </c>
-      <c r="I32" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="126" customHeight="1">
-      <c r="A33" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B33" s="1" t="n">
+      <c r="I31" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="126" customHeight="1">
+      <c r="A32" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B32" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>準1</t>
         </is>
       </c>
-      <c r="D33" s="1" t="inlineStr">
+      <c r="D32" s="1" t="inlineStr">
         <is>
           <t>穴埋め形式</t>
         </is>
       </c>
-      <c r="E33" s="1" t="inlineStr">
+      <c r="E32" s="1" t="inlineStr">
         <is>
           <t>私たちは（ア）を使いお互いの感情や意思を伝えあっていますが（ア）よりも表情、視線、身振りなどのほうがより大切な役割を担っていることがあります。これらの（イ）にはメイクや服装、呼吸や（ウ）などもはいります。</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>1. 頭脳
 2. ことば
@@ -16934,46 +16891,46 @@
 8. メール</t>
         </is>
       </c>
-      <c r="G33" s="1" t="inlineStr">
+      <c r="G32" s="1" t="inlineStr">
         <is>
           <t>2,6,3</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="H32" s="11" t="inlineStr">
         <is>
           <t>(ア): 2. ことば (イ): 6. 非言語コミュニケーション (ウ): 3. 声の調子。言葉以外の手段を使って伝える非言語コミュニケーションをうまく使うことで相手により分かりやすく伝えることもあります。</t>
         </is>
       </c>
-      <c r="I33" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="126" customHeight="1">
-      <c r="A34" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B34" s="1" t="n">
+      <c r="I32" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="126" customHeight="1">
+      <c r="A33" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B33" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>準1</t>
         </is>
       </c>
-      <c r="D34" s="1" t="inlineStr">
+      <c r="D33" s="1" t="inlineStr">
         <is>
           <t>穴埋め形式</t>
         </is>
       </c>
-      <c r="E34" s="1" t="inlineStr">
+      <c r="E33" s="1" t="inlineStr">
         <is>
           <t>世界には数千もの言語があると言われていますがその伝達方法を見ると音声言語と（ア）言語に二分されます。音声言語は（イ）に依存するだけではありません。文字は音声言語を（ウ）したものです。そのため、文字はろう者も聞こえる人も双方が共通に利用できます。</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>1. 視覚化
 2. 視覚
@@ -16985,44 +16942,44 @@
 8. 手話</t>
         </is>
       </c>
-      <c r="G34" s="1" t="inlineStr">
+      <c r="G33" s="1" t="inlineStr">
         <is>
           <t>8,3,1</t>
         </is>
       </c>
-      <c r="H34" s="11" t="inlineStr">
+      <c r="H33" s="11" t="inlineStr">
         <is>
           <t>(ア): 8. 手話 (イ): 3. 聴覚 (ウ): 1. 視覚化。ろう者は音声言語を視覚化した文字を見て理解できますが耳から入る情報で文字の理解を深めたりすることができないこともあり、文字は苦手だという方がいます。聴覚で知る情報を視覚化すれば聞こえない人・聞こえにくい人はもちろん、聞こえる人にも優しい社会になるでしょう。</t>
         </is>
       </c>
-      <c r="I34" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="110.25" customHeight="1">
-      <c r="A35" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B35" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C35" s="1" t="n">
+      <c r="I33" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="126" customHeight="1">
+      <c r="A34" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C34" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D35" s="1" t="inlineStr">
+      <c r="D34" s="1" t="inlineStr">
         <is>
           <t>4択問題</t>
         </is>
       </c>
-      <c r="E35" s="1" t="inlineStr">
+      <c r="E34" s="1" t="inlineStr">
         <is>
           <t>きこえない・きこえにくい人ときこえる人との会話をオペレータが手話や文字、音声を使って電話通訳するサービスは何といいますか。</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>1. 電話リレーサービス
 2. 電話通訳ハローライン
@@ -17030,42 +16987,42 @@
 4. 多言語通訳サービス</t>
         </is>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="G34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H35" s="11" t="inlineStr">
+      <c r="H34" s="11" t="inlineStr">
         <is>
           <t>電話リレーサービスは、聴覚障害者等による電話の利用の円滑化に関する法律（令和2年法律第53号）に基づいたサービスです。電話通訳ハローラインは、通訳オペレータを介して外国語（音声言語）を電話で通訳するサービスです。ショートメッセージサービスは、携帯電話等の電話番号を宛先にメッセージ（文字）のやりとりをするサービスで、略してSMSとも呼ばれています。多言語通訳サービスは、電話やテレビ電話などを介して、外国語などを通訳するサービスで、消防署などに導入されている例があります。</t>
         </is>
       </c>
-      <c r="I35" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="141.75" customHeight="1">
-      <c r="A36" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C36" s="1" t="n">
+      <c r="I34" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="110.25" customHeight="1">
+      <c r="A35" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C35" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D36" s="1" t="inlineStr">
+      <c r="D35" s="1" t="inlineStr">
         <is>
           <t>4択問題</t>
         </is>
       </c>
-      <c r="E36" s="1" t="inlineStr">
+      <c r="E35" s="1" t="inlineStr">
         <is>
           <t>1974（昭和49）年に発足し、2024（令和6）年6月に創立50周年を迎えた全国組織で、全日本ろうあ連盟と連携して手話通訳等について全国レベルでの研究・交流を行う団体は、何といいますか。</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>1. 全国社会福祉協議会
 2. 全国手話通訳問題研究会
@@ -17073,85 +17030,42 @@
 4. 全国手話サークル連絡協議会</t>
         </is>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="G35" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H36" s="11" t="inlineStr">
+      <c r="H35" s="11" t="inlineStr">
         <is>
           <t>全国社会福祉協議会は、都道府県や市町村にある社会福祉協議会の活動を支援するとともに、全国的に共通する福祉課題に対応するため、国への各種提言や調査研究、広報、人材育成などの事業を行っている団体です。全国手話通訳者会議は、1968（昭和43）年6月2日に第1回の会議が福島県で開催されており、まだ数も少なかった手話通訳者の語り合う場を設けるために始まりました。全国手話サークル連絡協議会は、2024（令和6）年現在、存在していませんが、都道府県や地域によっては手話サークル間の交流の場であったり、ろうあ団体とともに活動する団体として、連絡協議会などが結成されています。</t>
         </is>
       </c>
-      <c r="I36" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="78.75" customHeight="1">
-      <c r="A37" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C37" s="1" t="n">
+      <c r="I35" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="141.75" customHeight="1">
+      <c r="A36" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C36" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D37" s="1" t="inlineStr">
+      <c r="D36" s="1" t="inlineStr">
         <is>
           <t>4択問題</t>
         </is>
       </c>
-      <c r="E37" s="1" t="inlineStr">
-        <is>
-          <t>1986（昭和61）年に、全国のろう者が宿泊に集まって開催された大会は何ですか。</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>1. ろう教育を考える全国討論集会
-2. 全国ろうあ青年大会
-3. 全国ろうあ婦人大会
-4. 全国ろうあ関東研究会</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H37" s="11" t="inlineStr">
-        <is>
-          <t>1986（昭和61）年に岐阜県で開催された全国ろうあ関東研究会は、座談会が中心と呼ばれていました。はじめて大きな会となり、全国からろう者が宿泊に集まって開催されました。これが後に全国規模に広がり、現在の全国ろうあ関東研究会となっています。文化、労働、福祉、教育などの内容で、保健や生活全般に関する課題を話し合う場として大切な役割を果たしています。</t>
-        </is>
-      </c>
-      <c r="I37" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="63" customHeight="1">
-      <c r="A38" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B38" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C38" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>4択問題</t>
-        </is>
-      </c>
-      <c r="E38" s="1" t="inlineStr">
+      <c r="E36" s="1" t="inlineStr">
         <is>
           <t>聴覚障害の種類のうち、内耳や聴神経の障害によって起こり、補聴器を使用しても音の聞き分けが難しいものはどれですか。</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>1. 感音性難聴
 2. 伝音性難聴
@@ -17159,42 +17073,42 @@
 4. 心因性難聴</t>
         </is>
       </c>
-      <c r="G38" s="2" t="n">
+      <c r="G36" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H38" s="11" t="inlineStr">
+      <c r="H36" s="11" t="inlineStr">
         <is>
           <t>感音性難聴は内耳や聴神経の障害が原因で起こる難聴です。音がひずんで聞こえたり、大きな音がうるさく感じたりする特徴があります。補聴器を使用しても音の聞き分けが難しい場合があります。一方、伝音性難聴は外耳や中耳の障害が原因で、補聴器の効果が得られやすいです。</t>
         </is>
       </c>
-      <c r="I38" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="63" customHeight="1">
-      <c r="A39" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B39" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C39" s="1" t="n">
+      <c r="I36" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="78.75" customHeight="1">
+      <c r="A37" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C37" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D39" s="1" t="inlineStr">
+      <c r="D37" s="1" t="inlineStr">
         <is>
           <t>4択問題</t>
         </is>
       </c>
-      <c r="E39" s="1" t="inlineStr">
+      <c r="E37" s="1" t="inlineStr">
         <is>
           <t>身体障害者福祉法において、聴覚障害者が認定される級で、両耳の聴力レベルが70デシベル以上のものは何級に当たりますか。</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>1. 2級
 2. 4級
@@ -17202,42 +17116,42 @@
 4. 3級</t>
         </is>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="G37" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H39" s="11" t="inlineStr">
+      <c r="H37" s="11" t="inlineStr">
         <is>
           <t>身体障害者福祉法において、両耳の聴力レベルが70デシベル以上の場合は6級に該当します。2級は両耳100デシベル以上、3級は90デシベル以上、4級は80デシベル以上が基準です。</t>
         </is>
       </c>
-      <c r="I39" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="63" customHeight="1">
-      <c r="A40" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B40" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C40" s="1" t="n">
+      <c r="I37" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="63" customHeight="1">
+      <c r="A38" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B38" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C38" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D40" s="1" t="inlineStr">
+      <c r="D38" s="1" t="inlineStr">
         <is>
           <t>4択問題</t>
         </is>
       </c>
-      <c r="E40" s="1" t="inlineStr">
+      <c r="E38" s="1" t="inlineStr">
         <is>
           <t>日本で最初のろう学校といわれているのはどこですか。</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>1. 東京盲唖院
 2. 京都盲唖院
@@ -17245,42 +17159,42 @@
 4. 名古屋盲唖院</t>
         </is>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="G38" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H40" s="11" t="inlineStr">
+      <c r="H38" s="11" t="inlineStr">
         <is>
           <t>1869（明治2）年、京都府立盲唖院が日本で初めて設立されたろう学校とされる。生活の場を提供するとともに、子どもたちに手話を教えながら読み書きを学ばせた。京都盲唖院は、後に京都府立聾学校と京都府立盲学校に分かれ、現在も存続している。</t>
         </is>
       </c>
-      <c r="I40" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="63" customHeight="1">
-      <c r="A41" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B41" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C41" s="1" t="n">
+      <c r="I38" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="63" customHeight="1">
+      <c r="A39" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B39" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C39" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D41" s="1" t="inlineStr">
+      <c r="D39" s="1" t="inlineStr">
         <is>
           <t>4択問題</t>
         </is>
       </c>
-      <c r="E41" s="1" t="inlineStr">
+      <c r="E39" s="1" t="inlineStr">
         <is>
           <t>「個人の心の問題」に障害の原因を帰す考え方であるモデルはどれですか。</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>1. ノーマライゼーション
 2. バリアフリー
@@ -17288,42 +17202,42 @@
 4. 医学モデル</t>
         </is>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="G39" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H41" s="11" t="inlineStr">
+      <c r="H39" s="11" t="inlineStr">
         <is>
           <t>医学モデルは、障害を個人の心身機能の障害に起因すると考える立場である。一方、社会モデルは社会のバリアを原因とし、バリアフリーやノーマライゼーションの理念が広がってきた。</t>
         </is>
       </c>
-      <c r="I41" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="63" customHeight="1">
-      <c r="A42" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B42" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C42" s="1" t="n">
+      <c r="I39" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="63" customHeight="1">
+      <c r="A40" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B40" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C40" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D42" s="1" t="inlineStr">
+      <c r="D40" s="1" t="inlineStr">
         <is>
           <t>4択問題</t>
         </is>
       </c>
-      <c r="E42" s="1" t="inlineStr">
+      <c r="E40" s="1" t="inlineStr">
         <is>
           <t>国民の障害者に関する理解と関心を深めるために制定された障害者週間は、毎年何月に実施されていますか。</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>1. 1月
 2. 8月
@@ -17331,42 +17245,42 @@
 4. 12月</t>
         </is>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="G40" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H42" s="11" t="inlineStr">
+      <c r="H40" s="11" t="inlineStr">
         <is>
           <t>障害者基本法（昭和45年法律第84号）に基づき、毎年12月3日から9日までを「障害者週間」と定めている。</t>
         </is>
       </c>
-      <c r="I42" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="63" customHeight="1">
-      <c r="A43" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B43" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C43" s="1" t="n">
+      <c r="I40" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="63" customHeight="1">
+      <c r="A41" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B41" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C41" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D43" s="1" t="inlineStr">
+      <c r="D41" s="1" t="inlineStr">
         <is>
           <t>4択問題</t>
         </is>
       </c>
-      <c r="E43" s="1" t="inlineStr">
+      <c r="E41" s="1" t="inlineStr">
         <is>
           <t>1963年に日本で最初の手話サークルといわれる「手話学習会みみずく」が設立されたのはどこですか。</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>1. 鳥取市
 2. 札幌市
@@ -17374,42 +17288,42 @@
 4. 京都市</t>
         </is>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="G41" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H43" s="11" t="inlineStr">
+      <c r="H41" s="11" t="inlineStr">
         <is>
           <t>1963年、京都市で「京都市手話学習会みみずく」が結成された。ろう者と健聴者が「一緒に話したい」という思いから始まり、現在も活動を続けている。</t>
         </is>
       </c>
-      <c r="I43" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="63" customHeight="1">
-      <c r="A44" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B44" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C44" s="1" t="n">
+      <c r="I41" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="63" customHeight="1">
+      <c r="A42" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B42" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C42" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D44" s="1" t="inlineStr">
+      <c r="D42" s="1" t="inlineStr">
         <is>
           <t>4択問題</t>
         </is>
       </c>
-      <c r="E44" s="1" t="inlineStr">
+      <c r="E42" s="1" t="inlineStr">
         <is>
           <t>1987年に聴覚障害者と視覚障害者のための高等教育機関として設立された大学の現在の名称はどれですか。</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>1. 日本障害者福祉大学
 2. 日本ろうあ者技術大学
@@ -17417,42 +17331,42 @@
 4. 筑波総合福祉大学</t>
         </is>
       </c>
-      <c r="G44" s="2" t="n">
+      <c r="G42" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H44" s="11" t="inlineStr">
+      <c r="H42" s="11" t="inlineStr">
         <is>
           <t>1978年に設置が検討され、1987年に聴覚障害者と視覚障害者のための高等教育機関として設立された。現在の名称は「筑波技術大学」である。</t>
         </is>
       </c>
-      <c r="I44" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="63" customHeight="1">
-      <c r="A45" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B45" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C45" s="1" t="n">
+      <c r="I42" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="63" customHeight="1">
+      <c r="A43" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B43" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C43" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D45" s="1" t="inlineStr">
+      <c r="D43" s="1" t="inlineStr">
         <is>
           <t>4択問題</t>
         </is>
       </c>
-      <c r="E45" s="1" t="inlineStr">
+      <c r="E43" s="1" t="inlineStr">
         <is>
           <t>聴覚障害者の主なコミュニケーション手段ではないものはどれですか。</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>1. 手話
 2. 筆談
@@ -17460,42 +17374,42 @@
 4. 点字</t>
         </is>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="G43" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H45" s="11" t="inlineStr">
+      <c r="H43" s="11" t="inlineStr">
         <is>
           <t>聴覚障害者の主なコミュニケーション手段には手話、筆談、指文字があり、点字は視覚障害者が用いるため該当しません。</t>
         </is>
       </c>
-      <c r="I45" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="63" customHeight="1">
-      <c r="A46" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B46" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C46" s="1" t="n">
+      <c r="I43" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="63" customHeight="1">
+      <c r="A44" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B44" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C44" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D46" s="1" t="inlineStr">
+      <c r="D44" s="1" t="inlineStr">
         <is>
           <t>4択問題</t>
         </is>
       </c>
-      <c r="E46" s="1" t="inlineStr">
+      <c r="E44" s="1" t="inlineStr">
         <is>
           <t>耳の構造は大きく分けて外耳、中耳、内耳、聴神経に分けられます。蝸牛はどの部位に当たりますか。</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>1. 外耳
 2. 中耳
@@ -17503,42 +17417,42 @@
 4. 聴神経</t>
         </is>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="G44" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H46" s="11" t="inlineStr">
+      <c r="H44" s="11" t="inlineStr">
         <is>
           <t>蝸牛は内耳に含まれる器官で、音の振動を電気信号に変換する役割を持ちます。</t>
         </is>
       </c>
-      <c r="I46" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="126" customHeight="1">
-      <c r="A47" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B47" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C47" s="1" t="n">
+      <c r="I44" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="63" customHeight="1">
+      <c r="A45" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B45" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C45" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D47" s="1" t="inlineStr">
+      <c r="D45" s="1" t="inlineStr">
         <is>
           <t>4択問題</t>
         </is>
       </c>
-      <c r="E47" s="1" t="inlineStr">
+      <c r="E45" s="1" t="inlineStr">
         <is>
           <t>1969（昭和44）年に、標準手話の普及のため「わたしたちの手話」が発行されました。標準手話の普及についての記述のうち、正しいのはどれですか。</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>1. 標準手話と地域の手話のどちらを使うかは地域のろう協会が決めた
 2. 標準手話と地域の手話、どちらも尊重する方針で普及した
@@ -17546,42 +17460,42 @@
 4. 地域では地域の手話だけ使えばよいので、標準手話はあまり普及しなかった</t>
         </is>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="G45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H47" s="11" t="inlineStr">
+      <c r="H45" s="11" t="inlineStr">
         <is>
           <t>「わたしたちの手話」は全国的に標準手話を普及させるために発行され、地域手話も尊重しつつ普及が進められました。</t>
         </is>
       </c>
-      <c r="I47" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="63" customHeight="1">
-      <c r="A48" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B48" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C48" s="1" t="n">
+      <c r="I45" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="63" customHeight="1">
+      <c r="A46" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B46" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C46" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D48" s="1" t="inlineStr">
+      <c r="D46" s="1" t="inlineStr">
         <is>
           <t>4択問題</t>
         </is>
       </c>
-      <c r="E48" s="1" t="inlineStr">
-        <is>
-          <t>2006（平成18）年12月に第6回国連総会で採択され、第2条の定義で「言語」とは音声言語及び手話その他の形態の非音声言語をいうと明記されたのはどれですか。</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="E46" s="1" t="inlineStr">
+        <is>
+          <t>2006（平成18）年12月に第61回国連総会で採択され、第2条の定義で「言語」とは音声言語及び手話その他の形態の非音声言語をいうと明記されたのはどれですか。</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>1. 障害者基本法
 2. 障害者差別解消法
@@ -17589,85 +17503,85 @@
 4. 障害者総合支援法</t>
         </is>
       </c>
-      <c r="G48" s="2" t="n">
+      <c r="G46" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H48" s="11" t="inlineStr">
+      <c r="H46" s="11" t="inlineStr">
         <is>
           <t>障害者権利条約では「言語」に手話を含めることが明記され、国際的に手話が言語として認知されました。</t>
         </is>
       </c>
-      <c r="I48" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="63" customHeight="1">
-      <c r="A49" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B49" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C49" s="1" t="n">
+      <c r="I46" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="126" customHeight="1">
+      <c r="A47" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C47" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D49" s="1" t="inlineStr">
+      <c r="D47" s="1" t="inlineStr">
         <is>
           <t>4択問題</t>
         </is>
       </c>
-      <c r="E49" s="1" t="inlineStr">
+      <c r="E47" s="1" t="inlineStr">
         <is>
           <t>次の語のうち、両手の形が同じになる手話表現はどれですか。</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>1. アルコール
 2. アルバイト
-3. アトラクション
+3. アルツハイマー
 4. アンケート</t>
         </is>
       </c>
-      <c r="G49" s="2" t="n">
+      <c r="G47" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H49" s="11" t="inlineStr">
-        <is>
-          <t>「アトラクション」は両手の人差し指を立て、顔の両脇でクルクルと同時に回す表現で、両手の形が同じになります。</t>
-        </is>
-      </c>
-      <c r="I49" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="63" customHeight="1">
-      <c r="A50" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B50" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C50" s="1" t="n">
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>「アルツハイマー」は両手の人差し指を立て、顔の両脇でクルクルと同時に回す表現で、両手の形が同じになります。</t>
+        </is>
+      </c>
+      <c r="I47" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="63" customHeight="1">
+      <c r="A48" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B48" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C48" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D50" s="1" t="inlineStr">
+      <c r="D48" s="1" t="inlineStr">
         <is>
           <t>4択問題</t>
         </is>
       </c>
-      <c r="E50" s="1" t="inlineStr">
+      <c r="E48" s="1" t="inlineStr">
         <is>
           <t>毎年9月23日は青色のライトアップが行われることがあります。この日は何に由来しますか。</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>1. 手話言語の国際デー
 2. 世界みみの日
@@ -17675,42 +17589,42 @@
 4. 国際ろうの日</t>
         </is>
       </c>
-      <c r="G50" s="2" t="n">
+      <c r="G48" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H50" s="11" t="inlineStr">
+      <c r="H48" s="11" t="inlineStr">
         <is>
           <t>9月23日は1951年に世界ろう連盟（WFD）が設立された日に由来し、2017年に国連で「手話言語の国際デー」と定められました。</t>
         </is>
       </c>
-      <c r="I50" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="63" customHeight="1">
-      <c r="A51" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B51" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C51" s="1" t="n">
+      <c r="I48" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="63" customHeight="1">
+      <c r="A49" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B49" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C49" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D51" s="1" t="inlineStr">
+      <c r="D49" s="1" t="inlineStr">
         <is>
           <t>4択問題</t>
         </is>
       </c>
-      <c r="E51" s="1" t="inlineStr">
+      <c r="E49" s="1" t="inlineStr">
         <is>
           <t>音の大きさ（強さ）の単位はどれですか。</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>1. ワット(W)　
 2. ヘルツ(Hz)　
@@ -17718,42 +17632,42 @@
 4. メートル(m)</t>
         </is>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="G49" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H51" s="11" t="inlineStr">
+      <c r="H49" s="11" t="inlineStr">
         <is>
           <t>音の大きさを表す単位はデシベル(dB)です。ワットは電力の単位、ヘルツは周波数、メートルは長さを表します。</t>
         </is>
       </c>
-      <c r="I51" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="110.25" customHeight="1">
-      <c r="A52" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B52" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C52" s="1" t="n">
+      <c r="I49" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="63" customHeight="1">
+      <c r="A50" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B50" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C50" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D52" s="1" t="inlineStr">
+      <c r="D50" s="1" t="inlineStr">
         <is>
           <t>4択問題</t>
         </is>
       </c>
-      <c r="E52" s="1" t="inlineStr">
+      <c r="E50" s="1" t="inlineStr">
         <is>
           <t>聴覚障害者のコミュニケーション手段について、正しいものはどれですか。</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>1. 補聴器をつけていれば、耳もとでささやき声でも必ず伝わる　
 2. 文字の読み書きが苦手な人もいるので、ひらがきだけで伝わる　
@@ -17761,128 +17675,42 @@
 4. 手話、筆談、身振り、指文字など多様な手段がある</t>
         </is>
       </c>
-      <c r="G52" s="2" t="n">
+      <c r="G50" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H52" s="11" t="inlineStr">
+      <c r="H50" s="11" t="inlineStr">
         <is>
           <t>聴覚障害者のコミュニケーションには手話・筆談・指文字・身振りなど多様な手段があります。個人差があるため一つの方法に限定することはできません。</t>
         </is>
       </c>
-      <c r="I52" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="63" customHeight="1">
-      <c r="A53" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B53" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C53" s="1" t="n">
+      <c r="I50" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="63" customHeight="1">
+      <c r="A51" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B51" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C51" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D53" s="1" t="inlineStr">
+      <c r="D51" s="1" t="inlineStr">
         <is>
           <t>4択問題</t>
         </is>
       </c>
-      <c r="E53" s="1" t="inlineStr">
-        <is>
-          <t>障害者基本法において、行政機関等や事業者に対して求めていることはどれですか。</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>1. 障害者の差別解消　
-2. 障害者の集団　
-3. 合同授業の提供　
-4. 手話は方言名であること</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53" s="11" t="inlineStr">
-        <is>
-          <t>障害者基本法は、障害者に対する差別解消を求めています。合理的配慮の提供を含め、共生社会の実現を目指しています。</t>
-        </is>
-      </c>
-      <c r="I53" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="63" customHeight="1">
-      <c r="A54" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B54" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C54" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>4択問題</t>
-        </is>
-      </c>
-      <c r="E54" s="1" t="inlineStr">
-        <is>
-          <t>2006年（平成18年）に手話言語研究所が設立された組織の名称はどれですか。</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>1. みなし手話研究所　
-2. 手話言語研究所　
-3. 全国耳研研究所　
-4. 全国手話ラボ</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H54" s="11" t="inlineStr">
-        <is>
-          <t>2006年に設立されたのは「手話言語研究所」です。全国ろうあ連盟に設置され、手話の研究・普及に取り組んでいます。</t>
-        </is>
-      </c>
-      <c r="I54" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="94.5" customHeight="1">
-      <c r="A55" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B55" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C55" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D55" s="1" t="inlineStr">
-        <is>
-          <t>4択問題</t>
-        </is>
-      </c>
-      <c r="E55" s="1" t="inlineStr">
+      <c r="E51" s="1" t="inlineStr">
         <is>
           <t>人工内耳に関する記述のうち、正しくないものはどれですか。</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>1. 人工内耳は音声信号を電気信号に変えるスピーチプロセッサが必要である　
 2. 人工内耳には外部装置が必要である　
@@ -17890,42 +17718,42 @@
 4. 人工内耳は耳の奥に電極を埋め込む</t>
         </is>
       </c>
-      <c r="G55" s="2" t="n">
+      <c r="G51" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H55" s="11" t="inlineStr">
+      <c r="H51" s="11" t="inlineStr">
         <is>
           <t>人工内耳は手術後もリハビリテーションが必要です。外部装置と組み合わせて音を認識できるようになります。</t>
         </is>
       </c>
-      <c r="I55" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="63" customHeight="1">
-      <c r="A56" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B56" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C56" s="1" t="n">
+      <c r="I51" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="110.25" customHeight="1">
+      <c r="A52" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B52" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C52" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D56" s="1" t="inlineStr">
+      <c r="D52" s="1" t="inlineStr">
         <is>
           <t>4択問題</t>
         </is>
       </c>
-      <c r="E56" s="1" t="inlineStr">
+      <c r="E52" s="1" t="inlineStr">
         <is>
           <t>道路交通法で定められた「聴覚障害者標識（マーク）」はどれですか。</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. 蝶々のような緑と黄色のマーク
 2. 四つ葉のクローバーの緑のマーク
@@ -17933,44 +17761,44 @@
 4. ハートマーク</t>
         </is>
       </c>
-      <c r="G56" s="2" t="n">
+      <c r="G52" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H56" s="11" t="inlineStr">
+      <c r="H52" s="11" t="inlineStr">
         <is>
           <t>聴覚障害者標識は蝶々のような形をした緑と黄色のマークです。2008年の道路交通法改正により導入されました。車に貼ることで周囲に配慮を促す役割を持ちます。なお、四つ葉のクローバーマークは身体障害者標識です。</t>
         </is>
       </c>
-      <c r="I56" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="157.5" customHeight="1">
-      <c r="A57" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B57" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="I52" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="63" customHeight="1">
+      <c r="A53" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B53" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>準1</t>
         </is>
       </c>
-      <c r="D57" s="1" t="inlineStr">
+      <c r="D53" s="1" t="inlineStr">
         <is>
           <t>穴埋め形式</t>
         </is>
       </c>
-      <c r="E57" s="1" t="inlineStr">
+      <c r="E53" s="1" t="inlineStr">
         <is>
           <t>ろう者にとって（ア）は大切なコミュニケーション手段です。そして、ろう者の情報保障として（イ）がある。（イ）には2種類ある。音声言語に変換するのは（ウ）、さらに音声を手話に翻訳するのは（エ）といいます。（ア）〜（エ）に入る語句を選びなさい。</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>1. 要約筆記
 2. 手話
@@ -17984,46 +17812,46 @@
 0. 言語的支援</t>
         </is>
       </c>
-      <c r="G57" s="1" t="inlineStr">
+      <c r="G53" s="1" t="inlineStr">
         <is>
           <t>2,7,4,5</t>
         </is>
       </c>
-      <c r="H57" s="11" t="inlineStr">
+      <c r="H53" s="11" t="inlineStr">
         <is>
           <t>（ア）手話／（イ）手話通訳の指示先＝聴覚障害／（ウ）手話通訳／（エ）音声通訳という対応。</t>
         </is>
       </c>
-      <c r="I57" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="126" customHeight="1">
-      <c r="A58" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B58" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="I53" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="63" customHeight="1">
+      <c r="A54" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B54" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>準1</t>
         </is>
       </c>
-      <c r="D58" s="1" t="inlineStr">
+      <c r="D54" s="1" t="inlineStr">
         <is>
           <t>穴埋め形式</t>
         </is>
       </c>
-      <c r="E58" s="1" t="inlineStr">
+      <c r="E54" s="1" t="inlineStr">
         <is>
           <t>手話の歴史は、フランスの（ア）が1760年にパリで設立したろう学校で系統化が始まったとされます。日本で最初のろう学校は（イ）です。（ウ）が1878年に設立しました。</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. ド・レペ
 2. 京都聾唖院
@@ -18035,46 +17863,46 @@
 8. 高橋器具</t>
         </is>
       </c>
-      <c r="G58" s="1" t="inlineStr">
+      <c r="G54" s="1" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
       </c>
-      <c r="H58" s="11" t="inlineStr">
+      <c r="H54" s="11" t="inlineStr">
         <is>
           <t>近代ろう教育の端緒はド・レペ（仏）。日本最初は1878（明治11）年の京都聾唖院。</t>
         </is>
       </c>
-      <c r="I58" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="157.5" customHeight="1">
-      <c r="A59" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B59" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="I54" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="94.5" customHeight="1">
+      <c r="A55" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B55" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>準1</t>
         </is>
       </c>
-      <c r="D59" s="1" t="inlineStr">
+      <c r="D55" s="1" t="inlineStr">
         <is>
           <t>穴埋め形式</t>
         </is>
       </c>
-      <c r="E59" s="1" t="inlineStr">
+      <c r="E55" s="1" t="inlineStr">
         <is>
           <t>（ア）は、聴覚や発話に困難のある人（きこえない人）と、きこえる人（聴覚障害等以外の人）との会話を通訳オペレータが（イ）または「文字」と「音声」を通訳することで、即時（ウ）につながることができる、法律に基づいた公共インフラとしてのサービスです。2020（令和2）年6月、「聴覚障害者等による電話の利用の円滑化に関する法律」が制定され制度化されました。</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. 電話リレーサービス
 2. FAXリレーサービス
@@ -18086,47 +17914,47 @@
 8. 一方向</t>
         </is>
       </c>
-      <c r="G59" s="1" t="inlineStr">
+      <c r="G55" s="1" t="inlineStr">
         <is>
           <t>1,5,7</t>
         </is>
       </c>
-      <c r="H59" s="11" t="inlineStr">
+      <c r="H55" s="11" t="inlineStr">
         <is>
           <t>民間サービスで行われてきた「電話リレーサービス」が、2020（令和2）年から公的サービスとして整備されました。聴覚障害者はネット回線を通じて、手話等で「電話リレーサービス提供機関」の通訳オペレータに意思を伝え、それを電話の相手方あるいは警察や消防等の緊急通報受理機関に音声等で伝えることで、双方が電話でコミュニケーションを取ることができます。
 このサービスはきこえる人が電話をいつでも使えるのと同様に、24時間・365日利用が可能です。利用料金もきこえる人の電話料等と変わりません。電話リレーサービスにかかる費用は、各電話会社により負担されており、携帯電話利用者の利用料に「電話リレーサービス料」として計上されています。</t>
         </is>
       </c>
-      <c r="I59" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="141.75" customHeight="1">
-      <c r="A60" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B60" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="I55" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="63" customHeight="1">
+      <c r="A56" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B56" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>準1</t>
         </is>
       </c>
-      <c r="D60" s="1" t="inlineStr">
+      <c r="D56" s="1" t="inlineStr">
         <is>
           <t>穴埋め形式</t>
         </is>
       </c>
-      <c r="E60" s="1" t="inlineStr">
+      <c r="E56" s="1" t="inlineStr">
         <is>
           <t>聴覚障害者活動は、ひとことで言えば、社会への（ア）をめざす取り組みといえます。多くの運動の成果として、「人権を守る活動」では、（イ）、民法第11条の改正、（ウ）があげられます。</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. 医師法等の絶対的欠格条項の改正
 2. エコツーリズム
@@ -18138,46 +17966,46 @@
 8. 手話言語の理解と普及</t>
         </is>
       </c>
-      <c r="G60" s="1" t="inlineStr">
+      <c r="G56" s="1" t="inlineStr">
         <is>
           <t>6,4,1</t>
         </is>
       </c>
-      <c r="H60" s="11" t="inlineStr">
+      <c r="H56" s="11" t="inlineStr">
         <is>
           <t>自動車運転免許獲得運動は、1968（昭和43）年の岩手県での聴覚障害者の運転免許裁判をきっかけに展開されました。裁判では敗訴したものの、1973（昭和48）年には「補聴器装着条件での運転を認める」という警察庁通達が出され、翌年の道路交通法の改正では、補聴器を装着しても全くきこえない者を対象に「聴覚障害者用表示」「特定後写鏡（ワイドミラーまたは補助ミラー）」の装着を条件に運転免許が可能になりました。その後2007（平成19）年の道路交通法改正により、装着条件が緩和され、2012（平成24）年には貨物車、2016（平成28）年には営業バス、タクシーも条件付きで運転できるようになりました。</t>
         </is>
       </c>
-      <c r="I60" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="126" customHeight="1">
-      <c r="A61" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B61" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="I56" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="157.5" customHeight="1">
+      <c r="A57" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B57" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>準1</t>
         </is>
       </c>
-      <c r="D61" s="1" t="inlineStr">
+      <c r="D57" s="1" t="inlineStr">
         <is>
           <t>穴埋め形式</t>
         </is>
       </c>
-      <c r="E61" s="1" t="inlineStr">
+      <c r="E57" s="1" t="inlineStr">
         <is>
           <t>手話の「思う」と「私」では（ア）が異なります。「売る」と「買う」では（イ）が異なり、「男」と「女」では（ウ）が異なります。このような例から、手話言語は一定の要素が複雑に組み合わさって構成されているといえます。</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. 手の位置
 2. 手の動き
@@ -18189,46 +18017,46 @@
 8. リズム</t>
         </is>
       </c>
-      <c r="G61" s="1" t="inlineStr">
+      <c r="G57" s="1" t="inlineStr">
         <is>
           <t>1,2,4</t>
         </is>
       </c>
-      <c r="H61" s="11" t="inlineStr">
+      <c r="H57" s="11" t="inlineStr">
         <is>
           <t>手話は、手の形（手のひらを含む）、手の位置、手の動きが構成要素になっています。「思う」と「私」は人差し指の手の形は同じですが、「思う」はこめかみの辺りを指し、「私」は胸の前や顔の前を指すので、手の位置が異なります。また、「売る」と「買う」は手の動きが逆で意味が分かれ、「男」と「女」は手の形が異なることで意味を区別します。</t>
         </is>
       </c>
-      <c r="I61" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="126" customHeight="1">
-      <c r="A62" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B62" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="I57" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="126" customHeight="1">
+      <c r="A58" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B58" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>準1</t>
         </is>
       </c>
-      <c r="D62" s="1" t="inlineStr">
+      <c r="D58" s="1" t="inlineStr">
         <is>
           <t>穴埋め形式</t>
         </is>
       </c>
-      <c r="E62" s="1" t="inlineStr">
+      <c r="E58" s="1" t="inlineStr">
         <is>
           <t>全日本ろうあ運動が権利獲得のため取り組んだ運動は様々あります。1985（昭和60）年に（ア）制度化を提言するため厚生省（当時）に提出した報告をもとに作成されたパンフレット（イ）普及の取り組みは、当時の人口の約1％である（ウ）を想定して行われました。</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. 手話認定
 2. 手話通訳
@@ -18240,46 +18068,46 @@
 8. 15万部</t>
         </is>
       </c>
-      <c r="G62" s="1" t="inlineStr">
+      <c r="G58" s="1" t="inlineStr">
         <is>
           <t>2,3,7</t>
         </is>
       </c>
-      <c r="H62" s="11" t="inlineStr">
+      <c r="H58" s="11" t="inlineStr">
         <is>
           <t>手話通訳者の養成、設置・派遣の方法、全国統一の資格認定の必要性などをまとめた「手話通訳者養成指導者報告書」の内容を国民に広く理解してもらう目的で作成されたのが『アイ・ラブ・コミュニケーション』パンフレットです。普及活動は日本の人口の約1％に読んでもらうことを目標にしており、120万部を普及目標として印刷・配布されました。</t>
         </is>
       </c>
-      <c r="I62" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="157.5" customHeight="1">
-      <c r="A63" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B63" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="I58" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="157.5" customHeight="1">
+      <c r="A59" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B59" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>準1</t>
         </is>
       </c>
-      <c r="D63" s="1" t="inlineStr">
+      <c r="D59" s="1" t="inlineStr">
         <is>
           <t>穴埋め形式</t>
         </is>
       </c>
-      <c r="E63" s="1" t="inlineStr">
+      <c r="E59" s="1" t="inlineStr">
         <is>
           <t>きこえにくい状態を「難聴」と言います。難聴の種類には伝音性難聴と（ア）難聴、混合性難聴があります。聴力が最大で70デシベルを超えない伝音系のみに障害のある場合は、（イ）に音のエネルギーが伝わりにくくなるだけで、（ウ）の利用は有効です。</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. 遺伝性
 2. 補聴器
@@ -18293,46 +18121,46 @@
 0. 内耳</t>
         </is>
       </c>
-      <c r="G63" s="1" t="inlineStr">
+      <c r="G59" s="1" t="inlineStr">
         <is>
           <t>4,10,2</t>
         </is>
       </c>
-      <c r="H63" s="11" t="inlineStr">
+      <c r="H59" s="11" t="inlineStr">
         <is>
           <t>伝音性難聴は、外耳道から鼓膜、耳小骨までの外耳や中耳に原因があり、音のエネルギー（空気振動の伝導）が内耳に届きにくくなるものです。この場合、補聴器を使用すれば有効であり、多くの人にとって適切に音を拡大して伝えることができます。一方、感音性難聴は、内耳の有毛細胞や聴神経に障害があるために起こるきこえにくさを指します。</t>
         </is>
       </c>
-      <c r="I63" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="126" customHeight="1">
-      <c r="A64" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B64" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="I59" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="141.75" customHeight="1">
+      <c r="A60" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B60" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>準1</t>
         </is>
       </c>
-      <c r="D64" s="1" t="inlineStr">
+      <c r="D60" s="1" t="inlineStr">
         <is>
           <t>穴埋め形式</t>
         </is>
       </c>
-      <c r="E64" s="1" t="inlineStr">
+      <c r="E60" s="1" t="inlineStr">
         <is>
           <t>障害者福祉制度は、2003（平成15）年4月の（ア）の導入により、従来の「措置制度」から大きく転換されましたが、新たな課題が生じてきました。これらの課題の解決をめざし、2005（平成17）年11月に（イ）が公布されました。さらに2013（平成25）年4月に（ウ）となり、障害者に対する支援の拡充などの改正が行われました。</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. 支援費制度
 2. 障害者自立支援法
@@ -18344,46 +18172,46 @@
 8. 公費負担制度</t>
         </is>
       </c>
-      <c r="G64" s="1" t="inlineStr">
+      <c r="G60" s="1" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
       </c>
-      <c r="H64" s="11" t="inlineStr">
+      <c r="H60" s="11" t="inlineStr">
         <is>
           <t>戦後日本の障害者福祉制度は、行政が利用先や内容を決める「措置制度」で運営されていましたが、2003年に「支援費制度」が導入され、利用者自身が選択できる方式に変わりました。しかし課題も多く、2005年には「障害者自立支援法」が制定され、さらに2013年には「障害者総合支援法」に改正され、支援の拡充が図られました。</t>
         </is>
       </c>
-      <c r="I64" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="378" customHeight="1">
-      <c r="A65" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B65" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C65" s="1" t="n">
+      <c r="I60" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="126" customHeight="1">
+      <c r="A61" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B61" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C61" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D65" s="1" t="inlineStr">
+      <c r="D61" s="1" t="inlineStr">
         <is>
           <t>小論文</t>
         </is>
       </c>
-      <c r="E65" s="1" t="inlineStr">
+      <c r="E61" s="1" t="inlineStr">
         <is>
           <t>「障害者差別解消法にある合理的配慮について、聞こえない・聞こえにくい人が必要とすることは何ですか」</t>
         </is>
       </c>
-      <c r="F65" s="1" t="n"/>
-      <c r="G65" s="1" t="n"/>
-      <c r="H65" s="11" t="inlineStr">
+      <c r="F61" s="1" t="n"/>
+      <c r="G61" s="1" t="n"/>
+      <c r="H61" s="11" t="inlineStr">
         <is>
           <t>- 序論（導入）
   - 法律やテーマの概要を簡潔に説明する
@@ -18406,36 +18234,36 @@
   - これを整えることで誰もが安心して生活できる共生社会の実現につながる</t>
         </is>
       </c>
-      <c r="I65" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="409.5" customHeight="1">
-      <c r="A66" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B66" s="1" t="n">
+      <c r="I61" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="126" customHeight="1">
+      <c r="A62" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B62" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C62" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D66" s="1" t="inlineStr">
+      <c r="D62" s="1" t="inlineStr">
         <is>
           <t>小論文</t>
         </is>
       </c>
-      <c r="E66" s="1" t="inlineStr">
+      <c r="E62" s="1" t="inlineStr">
         <is>
           <t>「聴覚障害者が、さまざまな分野で社会参加するためにどのようなことが必要だと思いますか。」</t>
         </is>
       </c>
-      <c r="F66" s="1" t="n"/>
-      <c r="G66" s="1" t="n"/>
-      <c r="H66" s="11" t="inlineStr">
+      <c r="F62" s="1" t="n"/>
+      <c r="G62" s="1" t="n"/>
+      <c r="H62" s="11" t="inlineStr">
         <is>
           <t>- 序論（導入）
   - 聴覚障害者の社会参加の意義を述べる
@@ -18457,36 +18285,36 @@
   - それらを進めることが、多様性を尊重する豊かな社会の実現につながる</t>
         </is>
       </c>
-      <c r="I66" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="409.5" customHeight="1">
-      <c r="A67" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B67" s="1" t="n">
+      <c r="I62" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="157.5" customHeight="1">
+      <c r="A63" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B63" s="1" t="n">
         <v>2021</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C63" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D67" s="1" t="inlineStr">
+      <c r="D63" s="1" t="inlineStr">
         <is>
           <t>小論文</t>
         </is>
       </c>
-      <c r="E67" s="1" t="inlineStr">
+      <c r="E63" s="1" t="inlineStr">
         <is>
           <t>「「共生社会」という言葉がよく使われています。聴覚障害者が暮らしやすい社会になるために必要と考えることを述べてください。」</t>
         </is>
       </c>
-      <c r="F67" s="1" t="n"/>
-      <c r="G67" s="1" t="n"/>
-      <c r="H67" s="11" t="inlineStr">
+      <c r="F63" s="1" t="n"/>
+      <c r="G63" s="1" t="n"/>
+      <c r="H63" s="11" t="inlineStr">
         <is>
           <t>- 序論（導入）
   - 「共生社会」の意味を簡潔に説明する
@@ -18508,36 +18336,36 @@
   - 共生社会の実現は、誰もが安心して暮らせる未来につながる</t>
         </is>
       </c>
-      <c r="I67" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="409.5" customHeight="1">
-      <c r="A68" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B68" s="1" t="n">
+      <c r="I63" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="126" customHeight="1">
+      <c r="A64" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B64" s="1" t="n">
         <v>2020</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C64" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D68" s="1" t="inlineStr">
+      <c r="D64" s="1" t="inlineStr">
         <is>
           <t>小論文</t>
         </is>
       </c>
-      <c r="E68" s="1" t="inlineStr">
+      <c r="E64" s="1" t="inlineStr">
         <is>
           <t>「新しい手話の創作と普及について、あなたの考えを述べてください。」</t>
         </is>
       </c>
-      <c r="F68" s="1" t="n"/>
-      <c r="G68" s="1" t="n"/>
-      <c r="H68" s="11" t="inlineStr">
+      <c r="F64" s="1" t="n"/>
+      <c r="G64" s="1" t="n"/>
+      <c r="H64" s="11" t="inlineStr">
         <is>
           <t>- 序論（導入）
   - 手話は時代や社会の変化に応じて新しい語彙が生まれる言語であることを述べる
@@ -18563,36 +18391,36 @@
   - ろう者が主体となり、社会全体で支える仕組みを整えることが重要である</t>
         </is>
       </c>
-      <c r="I68" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="409.5" customHeight="1">
-      <c r="A69" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B69" s="1" t="n">
+      <c r="I64" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="378" customHeight="1">
+      <c r="A65" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B65" s="1" t="n">
         <v>2019</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C65" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D69" s="1" t="inlineStr">
+      <c r="D65" s="1" t="inlineStr">
         <is>
           <t>小論文</t>
         </is>
       </c>
-      <c r="E69" s="1" t="inlineStr">
+      <c r="E65" s="1" t="inlineStr">
         <is>
           <t>「聴覚障害者の雇用について、あなたの考えを書いてください。」</t>
         </is>
       </c>
-      <c r="F69" s="1" t="n"/>
-      <c r="G69" s="1" t="n"/>
-      <c r="H69" s="11" t="inlineStr">
+      <c r="F65" s="1" t="n"/>
+      <c r="G65" s="1" t="n"/>
+      <c r="H65" s="11" t="inlineStr">
         <is>
           <t>- 序論（導入）
   - 雇用は自立と社会参加の基盤であることを示す
@@ -18615,36 +18443,36 @@
   - 働きやすい環境を整えることは、個人の自立と社会全体の持続的発展に結びつく</t>
         </is>
       </c>
-      <c r="I69" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="409.5" customHeight="1">
-      <c r="A70" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B70" s="1" t="n">
+      <c r="I65" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="409.5" customHeight="1">
+      <c r="A66" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B66" s="1" t="n">
         <v>2018</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C66" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D70" s="1" t="inlineStr">
+      <c r="D66" s="1" t="inlineStr">
         <is>
           <t>小論文</t>
         </is>
       </c>
-      <c r="E70" s="1" t="inlineStr">
+      <c r="E66" s="1" t="inlineStr">
         <is>
           <t>「障害のある人が暮らしやすい社会の実現のために何が必要だと考えますか。あなたの考えを述べてください。」</t>
         </is>
       </c>
-      <c r="F70" s="1" t="n"/>
-      <c r="G70" s="1" t="n"/>
-      <c r="H70" s="11" t="inlineStr">
+      <c r="F66" s="1" t="n"/>
+      <c r="G66" s="1" t="n"/>
+      <c r="H66" s="11" t="inlineStr">
         <is>
           <t>- 序論（導入）
   - 障害の有無にかかわらず誰もが安心して暮らせる社会の重要性を示す
@@ -18667,36 +18495,36 @@
   - それを社会全体で支えることで、誰もが共に生きやすい未来が実現する</t>
         </is>
       </c>
-      <c r="I70" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="409.5" customHeight="1">
-      <c r="A71" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B71" s="1" t="n">
+      <c r="I66" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="409.5" customHeight="1">
+      <c r="A67" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B67" s="1" t="n">
         <v>2017</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C67" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D71" s="1" t="inlineStr">
+      <c r="D67" s="1" t="inlineStr">
         <is>
           <t>小論文</t>
         </is>
       </c>
-      <c r="E71" s="1" t="inlineStr">
+      <c r="E67" s="1" t="inlineStr">
         <is>
           <t>「障害者差別解消法が施行されて一年半が過ぎましたが、障害者の暮らしはどのように変わりましたか。また変わってほしいですか。あなたの考えを書いてください。」</t>
         </is>
       </c>
-      <c r="F71" s="1" t="n"/>
-      <c r="G71" s="1" t="n"/>
-      <c r="H71" s="11" t="inlineStr">
+      <c r="F67" s="1" t="n"/>
+      <c r="G67" s="1" t="n"/>
+      <c r="H67" s="11" t="inlineStr">
         <is>
           <t>- 序論（導入）
   - 障害者差別解消法の目的を簡潔に示す
@@ -18720,36 +18548,36 @@
   - 今後は法律を形式的に守る段階から、社会全体で障害者の視点を共有する段階へ進む必要がある</t>
         </is>
       </c>
-      <c r="I71" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="409.5" customHeight="1">
-      <c r="A72" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B72" s="1" t="n">
+      <c r="I67" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="409.5" customHeight="1">
+      <c r="A68" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B68" s="1" t="n">
         <v>2016</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C68" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D72" s="1" t="inlineStr">
+      <c r="D68" s="1" t="inlineStr">
         <is>
           <t>小論文</t>
         </is>
       </c>
-      <c r="E72" s="1" t="inlineStr">
+      <c r="E68" s="1" t="inlineStr">
         <is>
           <t>「今年の４月から障害者差別解消法が施行されましたが、聞こえない人が社会の中で暮らすためにどのような環境になればよいと思いますか。あなたの考えを書いてください。」</t>
         </is>
       </c>
-      <c r="F72" s="1" t="n"/>
-      <c r="G72" s="1" t="n"/>
-      <c r="H72" s="11" t="inlineStr">
+      <c r="F68" s="1" t="n"/>
+      <c r="G68" s="1" t="n"/>
+      <c r="H68" s="11" t="inlineStr">
         <is>
           <t>- 序論（導入）
   - 法律の施行を契機に、社会全体が変化を求められていることを示す
@@ -18772,36 +18600,36 @@
   - 法律をきっかけに、社会全体が理解と実践を進めることが重要である</t>
         </is>
       </c>
-      <c r="I72" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="409.5" customHeight="1">
-      <c r="A73" s="1">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B73" s="1" t="n">
+      <c r="I68" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="409.5" customHeight="1">
+      <c r="A69" s="1">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B69" s="1" t="n">
         <v>2015</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C69" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D73" s="1" t="inlineStr">
+      <c r="D69" s="1" t="inlineStr">
         <is>
           <t>小論文</t>
         </is>
       </c>
-      <c r="E73" s="1" t="inlineStr">
+      <c r="E69" s="1" t="inlineStr">
         <is>
           <t>「あなたの会社（学校・クラス）に聴覚障害のある人が入ってきました。この聴覚障害者が快適に仕事（学校）をするために、どのような配慮が必要と考えるか述べてください。」</t>
         </is>
       </c>
-      <c r="F73" s="1" t="n"/>
-      <c r="G73" s="1" t="n"/>
-      <c r="H73" s="11" t="inlineStr">
+      <c r="F69" s="1" t="n"/>
+      <c r="G69" s="1" t="n"/>
+      <c r="H69" s="11" t="inlineStr">
         <is>
           <t>- 序論（導入）
   - 新しい仲間が加わる場面を想定し、配慮の必要性を示す
@@ -18826,12 +18654,16 @@
   - これらを整えることで、聴覚障害者が快適に活動でき、共に成長する環境が実現する</t>
         </is>
       </c>
-      <c r="I73" s="1" t="inlineStr">
-        <is>
-          <t>KatsuoShuwaDoga</t>
-        </is>
-      </c>
-    </row>
+      <c r="I69" s="1" t="inlineStr">
+        <is>
+          <t>KatsuoShuwaDoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="409.5" customHeight="1"/>
+    <row r="71" ht="409.5" customHeight="1"/>
+    <row r="72" ht="409.5" customHeight="1"/>
+    <row r="73" ht="409.5" customHeight="1"/>
   </sheetData>
   <autoFilter ref="A1:I65"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
